--- a/output/full_scan/batch_seq8_2026-07-23.xlsx
+++ b/output/full_scan/batch_seq8_2026-07-23.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -580,21 +580,21 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6863</v>
+        <v>7714</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>763.9595350346434</v>
+        <v>782.0216768962126</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>109.5</v>
+        <v>177</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>66.30149379386219</v>
+        <v>55.26913004204766</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>25.89126508348967</v>
+        <v>39.29409453328878</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.995953503464336</v>
+        <v>0.4857359961890165</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>1.657980579131403</v>
+        <v>0.2831886479284584</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>8039</v>
+        <v>6863</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>702.358298387545</v>
+        <v>763.9595350346434</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>256</v>
+        <v>109.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>81.90744041114999</v>
+        <v>66.30149379386219</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>33.15890041307981</v>
+        <v>25.89126508348967</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2.335829838754501</v>
+        <v>1.995953503464336</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>9.145621062338549</v>
+        <v>1.657980579131403</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6957</v>
+        <v>8039</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>裕慶-KY</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>688.2965573821025</v>
+        <v>702.358298387545</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,13 +711,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>70.66895073391953</v>
+        <v>81.90744041114999</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>50.4112718469684</v>
+        <v>33.15890041307981</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.374394682751189</v>
+        <v>2.335829838754501</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>2.844931625452149</v>
+        <v>9.145621062338549</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6922</v>
+        <v>6957</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>裕慶-KY</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>684.5393259500897</v>
+        <v>688.2965573821025</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>194.5</v>
+        <v>243</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>61.19077887192923</v>
+        <v>70.66895073391953</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>16.28253791544083</v>
+        <v>50.4112718469684</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.3491884574862</v>
+        <v>1.374394682751189</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>2.041256477936195</v>
+        <v>2.844931625452149</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6949</v>
+        <v>6907</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>680.2704978824196</v>
+        <v>686.8273991805552</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1005</v>
+        <v>217</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>60.50052288381234</v>
+        <v>61.84662837275646</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>39.17350181263283</v>
+        <v>37.72220112207582</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.4474654892086703</v>
+        <v>0.242637417777514</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.6393843631825362</v>
+        <v>1.160178028996022</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -845,21 +845,21 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6901</v>
+        <v>6922</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>629.2679264741568</v>
+        <v>684.5393259500897</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>17.15</v>
+        <v>194.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>45.2117832892825</v>
+        <v>61.19077887192923</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>39.18653195122948</v>
+        <v>16.28253791544083</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.2864589770735452</v>
+        <v>1.3491884574862</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.3994887226446291</v>
+        <v>2.041256477936195</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>7717</v>
+        <v>6949</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>595.8731913896968</v>
+        <v>680.2704978824196</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>461</v>
+        <v>1005</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>45.61471226780545</v>
+        <v>60.50052288381234</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>24.29039941828368</v>
+        <v>39.17350181263283</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.539957533248902</v>
+        <v>0.4474654892086703</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>5.966954049687601</v>
+        <v>-0.6393843631825362</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6969</v>
+        <v>6901</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>583.7459943130312</v>
+        <v>629.2679264741568</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>35.05</v>
+        <v>17.15</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>74.69894455678644</v>
+        <v>45.2117832892825</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>23.16556881670632</v>
+        <v>39.18653195122948</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.474599431303128</v>
+        <v>0.2864589770735452</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1.025331639106743</v>
+        <v>-0.3994887226446291</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>7610</v>
+        <v>7717</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>聯友金屬-創</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>574.0342732836585</v>
+        <v>595.8731913896968</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1655</v>
+        <v>461</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>36.01717915344641</v>
+        <v>45.61471226780545</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>29.72404319643352</v>
+        <v>24.29039941828368</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.478350859660228</v>
+        <v>1.539957533248902</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-126.9223855929564</v>
+        <v>5.966954049687601</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7795</v>
+        <v>6969</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>長廣</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>556.9368738364223</v>
+        <v>583.7459943130312</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>411</v>
+        <v>35.05</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>38.97436511176652</v>
+        <v>74.69894455678644</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>25.547210216687</v>
+        <v>23.16556881670632</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.5484967443898854</v>
+        <v>2.474599431303128</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-25.07468775142926</v>
+        <v>1.025331639106743</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8046</v>
+        <v>7610</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>535.6148677163441</v>
+        <v>574.0342732836585</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1230</v>
+        <v>1655</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>55.76775954978049</v>
+        <v>36.01717915344641</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>17.96435702646345</v>
+        <v>29.72404319643352</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.97551178445604</v>
+        <v>2.478350859660228</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-5.341486425409656</v>
+        <v>-126.9223855929564</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8024</v>
+        <v>7795</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>528.69354220811</v>
+        <v>556.9368738364223</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>15.7</v>
+        <v>411</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>52.49867480431847</v>
+        <v>38.97436511176652</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>32.33063472034234</v>
+        <v>25.547210216687</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.2236423773231148</v>
+        <v>0.5484967443898854</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-0.1923848476153957</v>
+        <v>-25.07468775142926</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>7828</v>
+        <v>8046</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>創新服務</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>509.0530624077048</v>
+        <v>535.6148677163441</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1890</v>
+        <v>1230</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>48.66148247770944</v>
+        <v>55.76775954978049</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>21.59317978483593</v>
+        <v>17.96435702646345</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.6300262556540088</v>
+        <v>0.97551178445604</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-42.06901639653552</v>
+        <v>-5.341486425409656</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6934</v>
+        <v>8024</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>501.1900542673396</v>
+        <v>528.69354220811</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>79.8</v>
+        <v>15.7</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>62.479350086061</v>
+        <v>52.49867480431847</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>21.85689952163919</v>
+        <v>32.33063472034234</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.0166764488706287</v>
+        <v>0.2236423773231148</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.7141332312653099</v>
+        <v>-0.1923848476153957</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8016</v>
+        <v>7828</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>497.3155816766759</v>
+        <v>509.0530624077048</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>298</v>
+        <v>1890</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>46.62949801305696</v>
+        <v>48.66148247770944</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>23.72279349625609</v>
+        <v>21.59317978483593</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.346753388152959</v>
+        <v>0.6300262556540088</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-5.726244462295091</v>
+        <v>-42.06901639653552</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>7715</v>
+        <v>6934</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>494.4838731435898</v>
+        <v>501.1900542673396</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>32.2</v>
+        <v>79.8</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>44.99598623780923</v>
+        <v>62.479350086061</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>32.24672887416185</v>
+        <v>21.85689952163919</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.3923278567326018</v>
+        <v>0.0166764488706287</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.5474174095382365</v>
+        <v>0.7141332312653099</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6937</v>
+        <v>8016</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>474.3297885687688</v>
+        <v>497.3155816766759</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>56.79675294841397</v>
+        <v>46.62949801305696</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>11.34395507227148</v>
+        <v>23.72279349625609</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.252948673917714</v>
+        <v>0.346753388152959</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>3.456559104692948</v>
+        <v>-5.726244462295091</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7728</v>
+        <v>7715</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>472.4473494111047</v>
+        <v>494.4838731435898</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>627</v>
+        <v>32.2</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>39.39002476658117</v>
+        <v>44.99598623780923</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>12.13404448042175</v>
+        <v>32.24672887416185</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.4768645648719304</v>
+        <v>0.3923278567326018</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-1.100681412554149</v>
+        <v>-0.5474174095382365</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6928</v>
+        <v>6937</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>470.6093275459346</v>
+        <v>474.3297885687688</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>52.7</v>
+        <v>291</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>51.12167654631274</v>
+        <v>56.79675294841397</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>29.76033340861948</v>
+        <v>11.34395507227148</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.5176309972179338</v>
+        <v>1.252948673917714</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.1736581748932919</v>
+        <v>3.456559104692948</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6967</v>
+        <v>7728</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>468.4303118745025</v>
+        <v>472.4473494111047</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>75.5</v>
+        <v>627</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>53.59697277844625</v>
+        <v>39.39002476658117</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>19.10943718162189</v>
+        <v>12.13404448042175</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.6901249668756185</v>
+        <v>0.4768645648719304</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>3</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.3072345717966849</v>
+        <v>-1.100681412554149</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1640,21 +1640,21 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6913</v>
+        <v>6928</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>466.549088141557</v>
+        <v>470.6093275459346</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>126.5</v>
+        <v>52.7</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>52.37345735447347</v>
+        <v>51.12167654631274</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>11.65381764977154</v>
+        <v>29.76033340861948</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.3413752491565187</v>
+        <v>0.5176309972179338</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.6458321039856749</v>
+        <v>-0.1736581748932919</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8033</v>
+        <v>6967</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>雷虎</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>455.1888508768016</v>
+        <v>468.4303118745025</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>190.5</v>
+        <v>75.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>48.48244362702689</v>
+        <v>53.59697277844625</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>39.22121896992721</v>
+        <v>19.10943718162189</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.9716737757435524</v>
+        <v>0.6901249668756185</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-5.817694182456059</v>
+        <v>0.3072345717966849</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6965</v>
+        <v>6913</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>448.8055462295675</v>
+        <v>466.549088141557</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>78.90000000000001</v>
+        <v>126.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>47.53986872443235</v>
+        <v>52.37345735447347</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>27.86950899943439</v>
+        <v>11.65381764977154</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.5180279216668595</v>
+        <v>0.3413752491565187</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.0533496097215916</v>
+        <v>0.6458321039856749</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6870</v>
+        <v>8033</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>432.5945976313602</v>
+        <v>455.1888508768016</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>269</v>
+        <v>190.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>45.10064741659451</v>
+        <v>48.48244362702689</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>19.31726472108011</v>
+        <v>39.22121896992721</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.6302273093305407</v>
+        <v>0.9716737757435524</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-4.956537445246573</v>
+        <v>-5.817694182456059</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>7711</v>
+        <v>6965</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>430.1125973051525</v>
+        <v>448.8055462295675</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>305.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>39.35036476344148</v>
+        <v>47.53986872443235</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>29.60160003160326</v>
+        <v>27.86950899943439</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.4665496475667087</v>
+        <v>0.5180279216668595</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.9608889187569504</v>
+        <v>0.0533496097215916</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6958</v>
+        <v>6870</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>421.1590054413002</v>
+        <v>432.5945976313602</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>18</v>
+        <v>269</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>56.02318272774549</v>
+        <v>45.10064741659451</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>23.97197458258111</v>
+        <v>19.31726472108011</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.3499665677215406</v>
+        <v>0.6302273093305407</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.1234954607662328</v>
+        <v>-4.956537445246573</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>7744</v>
+        <v>7711</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>409.8883573443164</v>
+        <v>430.1125973051525</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>423</v>
+        <v>305.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>37.24283062571209</v>
+        <v>39.35036476344148</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>13.41759395228333</v>
+        <v>29.60160003160326</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.6763610651924343</v>
+        <v>0.4665496475667087</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-2.104915212751992</v>
+        <v>0.9608889187569504</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6919</v>
+        <v>6958</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>403.5640458346477</v>
+        <v>421.1590054413002</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>100.5</v>
+        <v>18</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>46.36499541969471</v>
+        <v>56.02318272774549</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>16.63570206052716</v>
+        <v>23.97197458258111</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.8458003215468107</v>
+        <v>0.3499665677215406</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.5239899572923934</v>
+        <v>0.1234954607662328</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>7736</v>
+        <v>7744</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>399.5826931781563</v>
+        <v>409.8883573443164</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>70.5</v>
+        <v>423</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>45.00021037131965</v>
+        <v>37.24283062571209</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>21.83965918173078</v>
+        <v>13.41759395228333</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.9053537941771392</v>
+        <v>0.6763610651924343</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.0574664670306105</v>
+        <v>-2.104915212751992</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6914</v>
+        <v>6919</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>395.3304463718687</v>
+        <v>403.5640458346477</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>145</v>
+        <v>100.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>54.52220345620897</v>
+        <v>46.36499541969471</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>13.73390855142312</v>
+        <v>16.63570206052716</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.5777090805587783</v>
+        <v>0.8458003215468107</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.1064958814539558</v>
+        <v>-0.5239899572923934</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6947</v>
+        <v>7736</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>台鎔科技</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>392.5950777783561</v>
+        <v>399.5826931781563</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>78.5</v>
+        <v>70.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>37.92560789541586</v>
+        <v>45.00021037131965</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>21.11740045117866</v>
+        <v>21.83965918173078</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.777344084922747</v>
+        <v>0.9053537941771392</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.4281175218560258</v>
+        <v>0.0574664670306105</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6869</v>
+        <v>6914</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>389.706701906939</v>
+        <v>395.3304463718687</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>67.7</v>
+        <v>145</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>37.58754241849205</v>
+        <v>54.52220345620897</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>21.047087081568</v>
+        <v>13.73390855142312</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.3077962695434849</v>
+        <v>0.5777090805587783</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.1138766786538667</v>
+        <v>0.1064958814539558</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>7805</v>
+        <v>6947</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>台鎔科技</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>386.710634604704</v>
+        <v>392.5950777783561</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>617</v>
+        <v>78.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>36.46546610399338</v>
+        <v>37.92560789541586</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>36.98639816322352</v>
+        <v>21.11740045117866</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.2611184421698349</v>
+        <v>1.777344084922747</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.1727832619693785</v>
+        <v>-0.4281175218560258</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7788</v>
+        <v>6869</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>382.9311324701743</v>
+        <v>389.706701906939</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>230</v>
+        <v>67.7</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>44.11115567125152</v>
+        <v>37.58754241849205</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>20.56157723804744</v>
+        <v>21.047087081568</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.3550983305377231</v>
+        <v>0.3077962695434849</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-4.480547680947025</v>
+        <v>0.1138766786538667</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6953</v>
+        <v>7805</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>373.3425691831519</v>
+        <v>386.710634604704</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>222</v>
+        <v>617</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>45.36685935866259</v>
+        <v>36.46546610399338</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>10.98846353151101</v>
+        <v>36.98639816322352</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.740026537526352</v>
+        <v>0.2611184421698349</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.2129947525174786</v>
+        <v>0.1727832619693785</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6944</v>
+        <v>7788</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>373.1713770806872</v>
+        <v>382.9311324701743</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>829</v>
+        <v>230</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>36.07341077659258</v>
+        <v>44.11115567125152</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>13.40916050401464</v>
+        <v>20.56157723804744</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>2.672043431762642</v>
+        <v>0.3550983305377231</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-12.01501534528548</v>
+        <v>-4.480547680947025</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>7839</v>
+        <v>6953</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>372.3416433993125</v>
+        <v>373.3425691831519</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>45.95</v>
+        <v>222</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>48.64306453676603</v>
+        <v>45.36685935866259</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>11.063546485408</v>
+        <v>10.98846353151101</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.7371326703018947</v>
+        <v>1.740026537526352</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.6070607734499829</v>
+        <v>-0.2129947525174786</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8042</v>
+        <v>6944</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>367.8369489829071</v>
+        <v>373.1713770806872</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>123.5</v>
+        <v>829</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>38.14115453772221</v>
+        <v>36.07341077659258</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>22.22425156288218</v>
+        <v>13.40916050401464</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.6830439258190624</v>
+        <v>2.672043431762642</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-7.511709082044284</v>
+        <v>-12.01501534528548</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8021</v>
+        <v>7839</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>尖點</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>365.1280009230827</v>
+        <v>372.3416433993125</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>406.5</v>
+        <v>45.95</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>38.62048752176644</v>
+        <v>48.64306453676603</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>18.93021904036053</v>
+        <v>11.063546485408</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2.402994017650951</v>
+        <v>0.7371326703018947</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-17.11230108108183</v>
+        <v>0.6070607734499829</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8040</v>
+        <v>8042</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>362.8935902707766</v>
+        <v>367.8369489829071</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>75.7</v>
+        <v>123.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>34.31439896323899</v>
+        <v>38.14115453772221</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>25.59959177746709</v>
+        <v>22.22425156288218</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.177136811280229</v>
+        <v>0.6830439258190624</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>1</v>
@@ -2690,7 +2690,7 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-2.266156550963014</v>
+        <v>-7.511709082044284</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2700,21 +2700,21 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>7712</v>
+        <v>8021</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>362.1802163268497</v>
+        <v>365.1280009230827</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>146</v>
+        <v>406.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>37.31058037701441</v>
+        <v>38.62048752176644</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>27.04111564247668</v>
+        <v>18.93021904036053</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.5316529034038053</v>
+        <v>2.402994017650951</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-6.189084514261845</v>
+        <v>-17.11230108108183</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6861</v>
+        <v>8040</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>361.4471859195691</v>
+        <v>362.8935902707766</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>214</v>
+        <v>75.7</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>29.8290618118194</v>
+        <v>34.31439896323899</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>24.21631528844675</v>
+        <v>25.59959177746709</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.3684527300666601</v>
+        <v>0.177136811280229</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-6.539861515298405</v>
+        <v>-2.266156550963014</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2806,21 +2806,21 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>7792</v>
+        <v>7712</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>344.9416160823493</v>
+        <v>362.1802163268497</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>216</v>
+        <v>146</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>34.47846907909984</v>
+        <v>37.31058037701441</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>28.86547158109266</v>
+        <v>27.04111564247668</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.9726102157057904</v>
+        <v>0.5316529034038053</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-1.742432752756557</v>
+        <v>-6.189084514261845</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6916</v>
+        <v>6861</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>342.761278903323</v>
+        <v>361.4471859195691</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>19.85</v>
+        <v>214</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>48.28566320032239</v>
+        <v>29.8290618118194</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>12.95034768531767</v>
+        <v>24.21631528844675</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.3550357091216322</v>
+        <v>0.3684527300666601</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.1138379898595769</v>
+        <v>-6.539861515298405</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>7799</v>
+        <v>7792</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>341.5409399888984</v>
+        <v>344.9416160823493</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>398.5</v>
+        <v>216</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>48.8804033711194</v>
+        <v>34.47846907909984</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>29.75497975121828</v>
+        <v>28.86547158109266</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.4205603216151746</v>
+        <v>0.9726102157057904</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-4.109422662570097</v>
+        <v>-1.742432752756557</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8043</v>
+        <v>6916</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>337.568662029842</v>
+        <v>342.761278903323</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>146</v>
+        <v>19.85</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>40.59018517953111</v>
+        <v>48.28566320032239</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>22.916772436323</v>
+        <v>12.95034768531767</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.5966525878272562</v>
+        <v>0.3550357091216322</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-5.32656744420329</v>
+        <v>-0.1138379898595769</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6997</v>
+        <v>7799</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>337.5664298465205</v>
+        <v>341.5409399888984</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>73</v>
+        <v>398.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>51.61280283388054</v>
+        <v>48.8804033711194</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>10.74478746309281</v>
+        <v>29.75497975121828</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.2506454119357345</v>
+        <v>0.4205603216151746</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.4268930669326121</v>
+        <v>-4.109422662570097</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6887</v>
+        <v>8043</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>336.9441532933023</v>
+        <v>337.568662029842</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>38.7</v>
+        <v>146</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>56.49547149608548</v>
+        <v>40.59018517953111</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>14.82861288143602</v>
+        <v>22.916772436323</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.1380115813660788</v>
+        <v>0.5966525878272562</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.2844141614581608</v>
+        <v>-5.32656744420329</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>7750</v>
+        <v>6997</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>335.3412338981109</v>
+        <v>337.5664298465205</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>2160</v>
+        <v>73</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>53.95554870490758</v>
+        <v>51.61280283388054</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>16.13137847932857</v>
+        <v>10.74478746309281</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.407970839038956</v>
+        <v>0.2506454119357345</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>13.39706727834451</v>
+        <v>-0.4268930669326121</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>7732</v>
+        <v>6887</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>334.4848544502506</v>
+        <v>336.9441532933023</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>35.75</v>
+        <v>38.7</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>51.77502909106067</v>
+        <v>56.49547149608548</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>7.185904811168576</v>
+        <v>14.82861288143602</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.7059144399611748</v>
+        <v>0.1380115813660788</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.3105819246812068</v>
+        <v>0.2844141614581608</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>7818</v>
+        <v>7750</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>334.0838483570053</v>
+        <v>335.3412338981109</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>68.7</v>
+        <v>2160</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>50.07579727977313</v>
+        <v>53.95554870490758</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>21.97731596818896</v>
+        <v>16.13137847932857</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.3159502234123536</v>
+        <v>1.407970839038956</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.3485506020133536</v>
+        <v>13.39706727834451</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6952</v>
+        <v>7732</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>330.1664803022178</v>
+        <v>334.4848544502506</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>35.55</v>
+        <v>35.75</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>46.8982045440002</v>
+        <v>51.77502909106067</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>16.24426324168845</v>
+        <v>7.185904811168576</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.16482649314867</v>
+        <v>0.7059144399611748</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.0604867740855045</v>
+        <v>0.3105819246812068</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>7768</v>
+        <v>7818</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>329.7452218233902</v>
+        <v>334.0838483570053</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>295</v>
+        <v>68.7</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>29.71766579388468</v>
+        <v>50.07579727977313</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>29.72946726962285</v>
+        <v>21.97731596818896</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.18796222891815</v>
+        <v>0.3159502234123536</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-3.723872239742896</v>
+        <v>0.3485506020133536</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6933</v>
+        <v>6952</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>325.1464198977187</v>
+        <v>330.1664803022178</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>167.5</v>
+        <v>35.55</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>54.69532202113573</v>
+        <v>46.8982045440002</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>12.51946316427749</v>
+        <v>16.24426324168845</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.639079009021202</v>
+        <v>1.16482649314867</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>1.982593298029829</v>
+        <v>0.0604867740855045</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6899</v>
+        <v>7768</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>316.8243245812903</v>
+        <v>329.7452218233902</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>51.3</v>
+        <v>295</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>29.34165637529632</v>
+        <v>29.71766579388468</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>26.3804536852973</v>
+        <v>29.72946726962285</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.6358523346322598</v>
+        <v>1.18796222891815</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.375768285440555</v>
+        <v>-3.723872239742896</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3495,21 +3495,21 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>7704</v>
+        <v>6933</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>316.5165797502977</v>
+        <v>325.1464198977187</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>53.1</v>
+        <v>167.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>33.6712970977886</v>
+        <v>54.69532202113573</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>22.8259115855756</v>
+        <v>12.51946316427749</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.3908518350420601</v>
+        <v>1.639079009021202</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.7307039113185052</v>
+        <v>1.982593298029829</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>7722</v>
+        <v>6899</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>314.3323996972015</v>
+        <v>316.8243245812903</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>297.5</v>
+        <v>51.3</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>44.51326728246337</v>
+        <v>29.34165637529632</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>24.16400762340985</v>
+        <v>26.3804536852973</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.4963532105658479</v>
+        <v>0.6358523346322598</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-2.305844389013287</v>
+        <v>-0.375768285440555</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6951</v>
+        <v>7704</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>314.3168551688958</v>
+        <v>316.5165797502977</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>72</v>
+        <v>53.1</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>32.09339628592001</v>
+        <v>33.6712970977886</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>33.09140678364429</v>
+        <v>22.8259115855756</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.3733028046994778</v>
+        <v>0.3908518350420601</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.3545678797373082</v>
+        <v>-0.7307039113185052</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>7749</v>
+        <v>7722</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>314.0370117654018</v>
+        <v>314.3323996972015</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>361</v>
+        <v>297.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>31.12012342749762</v>
+        <v>44.51326728246337</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>26.25574160242144</v>
+        <v>24.16400762340985</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.4632263841245727</v>
+        <v>0.4963532105658479</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-3.127355785372572</v>
+        <v>-2.305844389013287</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8032</v>
+        <v>6951</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>312.0461767421546</v>
+        <v>314.3168551688958</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>36.5</v>
+        <v>72</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>31.52015086310239</v>
+        <v>32.09339628592001</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>28.27012834047155</v>
+        <v>33.09140678364429</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.4015027152206254</v>
+        <v>0.3733028046994778</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.5003653707041347</v>
+        <v>-0.3545678797373082</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>7556</v>
+        <v>7749</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>309.1247534632197</v>
+        <v>314.0370117654018</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>220.5</v>
+        <v>361</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>32.04350969773647</v>
+        <v>31.12012342749762</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>28.06273099467625</v>
+        <v>26.25574160242144</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.4057888723277818</v>
+        <v>0.4632263841245727</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-4.838336133486365</v>
+        <v>-3.127355785372572</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>7823</v>
+        <v>8032</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>307.177635801612</v>
+        <v>312.0461767421546</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>83.90000000000001</v>
+        <v>36.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>48.61193690046223</v>
+        <v>31.52015086310239</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>23.27284018985618</v>
+        <v>28.27012834047155</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.2978697538853382</v>
+        <v>0.4015027152206254</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.45095515177868</v>
+        <v>-0.5003653707041347</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>7740</v>
+        <v>7556</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>303.2473964566036</v>
+        <v>309.1247534632197</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>157</v>
+        <v>220.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>49.64233714307193</v>
+        <v>32.04350969773647</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>15.23279946876004</v>
+        <v>28.06273099467625</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.055193389934544</v>
+        <v>0.4057888723277818</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>1.900264346156993</v>
+        <v>-4.838336133486365</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>7760</v>
+        <v>7823</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>300.1651461006807</v>
+        <v>307.177635801612</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>34.95</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>56.28772593247027</v>
+        <v>48.61193690046223</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>27.24894267187786</v>
+        <v>23.27284018985618</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.3469367486948004</v>
+        <v>0.2978697538853382</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.0466745174650531</v>
+        <v>0.45095515177868</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>7631</v>
+        <v>7740</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>299.7061236551083</v>
+        <v>303.2473964566036</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>46.81568050743376</v>
+        <v>49.64233714307193</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>11.16460621893039</v>
+        <v>15.23279946876004</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.068256309126702</v>
+        <v>1.055193389934544</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-2.773216867654547</v>
+        <v>1.900264346156993</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>7822</v>
+        <v>7760</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>299.64122159829</v>
+        <v>300.1651461006807</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>864</v>
+        <v>34.95</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>35.29856245368698</v>
+        <v>56.28772593247027</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>21.18797083302075</v>
+        <v>27.24894267187786</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.4523366283768053</v>
+        <v>0.3469367486948004</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-15.14515884206521</v>
+        <v>-0.0466745174650531</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>7821</v>
+        <v>7631</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>298.065744552442</v>
+        <v>299.7061236551083</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>40.6</v>
+        <v>139</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>40.35631884937752</v>
+        <v>46.81568050743376</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>24.5117113354021</v>
+        <v>11.16460621893039</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.6094957668766474</v>
+        <v>0.068256309126702</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.1032726504937169</v>
+        <v>-2.773216867654547</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>7786</v>
+        <v>7822</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>296.7366387335007</v>
+        <v>299.64122159829</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>129.5</v>
+        <v>864</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>52.93568207875568</v>
+        <v>35.29856245368698</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>13.84587240335939</v>
+        <v>21.18797083302075</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.257970452394338</v>
+        <v>0.4523366283768053</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.1871945241957131</v>
+        <v>-15.14515884206521</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>7772</v>
+        <v>7821</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>295.8551821884771</v>
+        <v>298.065744552442</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>99.2</v>
+        <v>40.6</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>30.29973862210683</v>
+        <v>40.35631884937752</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>22.17749693168862</v>
+        <v>24.5117113354021</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.2926677636951478</v>
+        <v>0.6094957668766474</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.970875956431124</v>
+        <v>0.1032726504937169</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6923</v>
+        <v>7786</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>293.7797990901055</v>
+        <v>296.7366387335007</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>78.5</v>
+        <v>129.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>52.14618392415719</v>
+        <v>52.93568207875568</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>12.73710090514093</v>
+        <v>13.84587240335939</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.656386292928833</v>
+        <v>1.257970452394338</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.2274551958658916</v>
+        <v>0.1871945241957131</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4290,21 +4290,21 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6909</v>
+        <v>7772</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>293.4468702290565</v>
+        <v>295.8551821884771</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>43.2</v>
+        <v>99.2</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>34.61766166141014</v>
+        <v>30.29973862210683</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>22.67677020192603</v>
+        <v>22.17749693168862</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.2208326707027951</v>
+        <v>0.2926677636951478</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-1.195895812139133</v>
+        <v>-0.970875956431124</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6994</v>
+        <v>6923</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>291.0539681597789</v>
+        <v>293.7797990901055</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>40.7</v>
+        <v>78.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>34.51766877047555</v>
+        <v>52.14618392415719</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>30.56089903114178</v>
+        <v>12.73710090514093</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.1803608201210072</v>
+        <v>0.656386292928833</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.3894117656159803</v>
+        <v>0.2274551958658916</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6873</v>
+        <v>6909</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>285.5618886355741</v>
+        <v>293.4468702290565</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>85.3</v>
+        <v>43.2</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>49.64045737385894</v>
+        <v>34.61766166141014</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>12.93897085962102</v>
+        <v>22.67677020192603</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.4714169000479765</v>
+        <v>0.2208326707027951</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0900535548213503</v>
+        <v>-1.195895812139133</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>7402</v>
+        <v>6994</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>275.0081254772982</v>
+        <v>291.0539681597789</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>110</v>
+        <v>40.7</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>44.67214165224655</v>
+        <v>34.51766877047555</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>24.4914300355689</v>
+        <v>30.56089903114178</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.4008125477298236</v>
+        <v>0.1803608201210072</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-2.97880622810234</v>
+        <v>0.3894117656159803</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>7810</v>
+        <v>6873</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>267.4889629405845</v>
+        <v>285.5618886355741</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>197</v>
+        <v>85.3</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>41.70716671492244</v>
+        <v>49.64045737385894</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>15.5215396983247</v>
+        <v>12.93897085962102</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.5383570052980498</v>
+        <v>0.4714169000479765</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.3466732689828884</v>
+        <v>0.0900535548213503</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6996</v>
+        <v>7402</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>266.0216520927446</v>
+        <v>275.0081254772982</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>178</v>
+        <v>110</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>42.52333232999591</v>
+        <v>44.67214165224655</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>22.20847094659787</v>
+        <v>24.4914300355689</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.1828803537806152</v>
+        <v>0.4008125477298236</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-1.927597330483017</v>
+        <v>-2.97880622810234</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>7780</v>
+        <v>7810</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>258.9792950725709</v>
+        <v>267.4889629405845</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>17.3</v>
+        <v>197</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>36.55580836004859</v>
+        <v>41.70716671492244</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>21.80276963846443</v>
+        <v>15.5215396983247</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.7613582283096205</v>
+        <v>0.5383570052980498</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0543785324369165</v>
+        <v>0.3466732689828884</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6962</v>
+        <v>6996</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>256.848470700526</v>
+        <v>266.0216520927446</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>32.95</v>
+        <v>178</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>37.97827968567307</v>
+        <v>42.52333232999591</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>21.62850335062642</v>
+        <v>22.20847094659787</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.4609981765473508</v>
+        <v>0.1828803537806152</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.4116736258684275</v>
+        <v>-1.927597330483017</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>7751</v>
+        <v>7780</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>256.6954763366584</v>
+        <v>258.9792950725709</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>1185</v>
+        <v>17.3</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>41.53934802369457</v>
+        <v>36.55580836004859</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>16.21456642229482</v>
+        <v>21.80276963846443</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.17156449899518</v>
+        <v>0.7613582283096205</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.3834520502753946</v>
+        <v>-0.0543785324369165</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>7791</v>
+        <v>6962</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>255.8915142120806</v>
+        <v>256.848470700526</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>62.1</v>
+        <v>32.95</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>43.44340135027886</v>
+        <v>37.97827968567307</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>13.00926278477134</v>
+        <v>21.62850335062642</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.6557736846065735</v>
+        <v>0.4609981765473508</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.0369237313923879</v>
+        <v>-0.4116736258684275</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>7769</v>
+        <v>7751</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>254.08701798625</v>
+        <v>256.6954763366584</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>6465</v>
+        <v>1185</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>47.8693189818672</v>
+        <v>41.53934802369457</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>12.12318185259457</v>
+        <v>16.21456642229482</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.7216199538966702</v>
+        <v>1.17156449899518</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-11.26700319734071</v>
+        <v>-0.3834520502753946</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4873,21 +4873,21 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6971</v>
+        <v>7791</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>253.4130382182654</v>
+        <v>255.8915142120806</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>27.05</v>
+        <v>62.1</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>45.12047988369245</v>
+        <v>43.44340135027886</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>20.58006089597773</v>
+        <v>13.00926278477134</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.5834708118742565</v>
+        <v>0.6557736846065735</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.0138191758062618</v>
+        <v>0.0369237313923879</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>7827</v>
+        <v>7769</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>251.5929041114928</v>
+        <v>254.08701798625</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>149</v>
+        <v>6465</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>41.22754606481023</v>
+        <v>47.8693189818672</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>16.12209316677698</v>
+        <v>12.12318185259457</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.2935681625874661</v>
+        <v>0.7216199538966702</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-2.781010577925126</v>
+        <v>-11.26700319734071</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -4979,21 +4979,21 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6902</v>
+        <v>6971</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>244.1257472689117</v>
+        <v>253.4130382182654</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>119</v>
+        <v>27.05</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>38.17723735574247</v>
+        <v>45.12047988369245</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>16.91391416465762</v>
+        <v>20.58006089597773</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.9927097656785756</v>
+        <v>0.5834708118742565</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-1.88302466124521</v>
+        <v>-0.0138191758062618</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6903</v>
+        <v>7827</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>243.3000491197991</v>
+        <v>251.5929041114928</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>362</v>
+        <v>149</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>44.80101299582062</v>
+        <v>41.22754606481023</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>14.25317955038643</v>
+        <v>16.12209316677698</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.3162140803179237</v>
+        <v>0.2935681625874661</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-3.124982785822702</v>
+        <v>-2.781010577925126</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6910</v>
+        <v>6902</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>238.1775906541541</v>
+        <v>244.1257472689117</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>24.5</v>
+        <v>119</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>26.59861727983052</v>
+        <v>38.17723735574247</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>32.0846021461515</v>
+        <v>16.91391416465762</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.9061907437713098</v>
+        <v>0.9927097656785756</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.175017874060526</v>
+        <v>-1.88302466124521</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>8011</v>
+        <v>6903</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>236.956122569167</v>
+        <v>243.3000491197991</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>16.45</v>
+        <v>362</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>38.78691839200054</v>
+        <v>44.80101299582062</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>23.72480375428752</v>
+        <v>14.25317955038643</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.7818867059713235</v>
+        <v>0.3162140803179237</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.0527651445407721</v>
+        <v>-3.124982785822702</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6885</v>
+        <v>6910</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>235.2348428834184</v>
+        <v>238.1775906541541</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>20.8</v>
+        <v>24.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>41.08793931441816</v>
+        <v>26.59861727983052</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>12.69680777461546</v>
+        <v>32.0846021461515</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.7670612496963201</v>
+        <v>0.9061907437713098</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.02468597465009</v>
+        <v>-0.175017874060526</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6862</v>
+        <v>8011</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>231.7421395122902</v>
+        <v>236.956122569167</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>148.5</v>
+        <v>16.45</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>35.55749992636382</v>
+        <v>38.78691839200054</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>19.49849302094121</v>
+        <v>23.72480375428752</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.3950741431485422</v>
+        <v>0.7818867059713235</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-3.656631219062945</v>
+        <v>-0.0527651445407721</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8045</v>
+        <v>6885</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>229.4339678629246</v>
+        <v>235.2348428834184</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>63.8</v>
+        <v>20.8</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>53.90173548731829</v>
+        <v>41.08793931441816</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>11.8836543680934</v>
+        <v>12.69680777461546</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.13040374032408</v>
+        <v>0.7670612496963201</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.9523324323071952</v>
+        <v>-0.02468597465009</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>7770</v>
+        <v>6862</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>221.0915035492424</v>
+        <v>231.7421395122901</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>40.45</v>
+        <v>148.5</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>40.96770772685456</v>
+        <v>35.55749992636382</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>9.145614907631776</v>
+        <v>19.49849302094121</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.1908870521312539</v>
+        <v>0.3950741431485422</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.1917298505591224</v>
+        <v>-3.656631219062945</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>7738</v>
+        <v>8045</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>216.7595167262392</v>
+        <v>229.4339678629246</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>170</v>
+        <v>63.8</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>52.10462630723484</v>
+        <v>53.90173548731829</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>24.36232661403211</v>
+        <v>11.8836543680934</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.717584922098025</v>
+        <v>1.13040374032408</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.1706779031082451</v>
+        <v>0.9523324323071952</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6924</v>
+        <v>7770</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>215.223121615217</v>
+        <v>221.0915035492424</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>104.5</v>
+        <v>40.45</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>36.49487413473683</v>
+        <v>40.96770772685456</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>16.47428383698991</v>
+        <v>9.145614907631776</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.305849355543185</v>
+        <v>0.1908870521312539</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-1.550286412765094</v>
+        <v>-0.1917298505591224</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>7820</v>
+        <v>7738</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>213.8001021210753</v>
+        <v>216.7595167262392</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>108</v>
+        <v>170</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>35.64090606354635</v>
+        <v>52.10462630723484</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>17.81024701722117</v>
+        <v>24.36232661403211</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.2734031828080371</v>
+        <v>0.717584922098025</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.3234899265371576</v>
+        <v>0.1706779031082451</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>7765</v>
+        <v>6924</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>212.7101520724881</v>
+        <v>215.223121615217</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>226</v>
+        <v>104.5</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>46.87333823764683</v>
+        <v>36.49487413473683</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>15.68452607465826</v>
+        <v>16.47428383698991</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.362718685096547</v>
+        <v>0.305849355543185</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>1.358404951358224</v>
+        <v>-1.550286412765094</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>7721</v>
+        <v>7820</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>208.2837067890667</v>
+        <v>213.8001021210753</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>63.4</v>
+        <v>108</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>37.07887987736241</v>
+        <v>35.64090606354635</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>16.2419897458733</v>
+        <v>17.81024701722117</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.2736292477128263</v>
+        <v>0.2734031828080371</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.651929015344956</v>
+        <v>-0.3234899265371576</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6936</v>
+        <v>7765</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>207.6041164998281</v>
+        <v>212.7101520724881</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>31.75</v>
+        <v>226</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>37.28396985275015</v>
+        <v>46.87333823764683</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>16.46631515836225</v>
+        <v>15.68452607465826</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.325832266069683</v>
+        <v>0.362718685096547</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.0548614698542188</v>
+        <v>1.358404951358224</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6854</v>
+        <v>7721</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>206.0109076871297</v>
+        <v>208.2837067890667</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>100.5</v>
+        <v>63.4</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>25.84259249298339</v>
+        <v>37.07887987736241</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>35.78064078796004</v>
+        <v>16.2419897458733</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.8142113636014991</v>
+        <v>0.2736292477128263</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.543638358136258</v>
+        <v>-0.651929015344956</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>7747</v>
+        <v>6936</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>205.3949199270637</v>
+        <v>207.6041164998281</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>115</v>
+        <v>31.75</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>41.49318085298187</v>
+        <v>37.28396985275015</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>16.42129272798803</v>
+        <v>16.46631515836225</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.328853199688669</v>
+        <v>1.325832266069683</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-1.205374466615639</v>
+        <v>-0.0548614698542188</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6894</v>
+        <v>6854</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>205.270124785197</v>
+        <v>206.0109076871297</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>327.5</v>
+        <v>100.5</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>40.5061992426077</v>
+        <v>25.84259249298339</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>16.94169642669102</v>
+        <v>35.78064078796004</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.6118846872729944</v>
+        <v>0.8142113636014991</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-2.912518678186893</v>
+        <v>-0.543638358136258</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6906</v>
+        <v>7747</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>205.2526191377197</v>
+        <v>205.3949199270637</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>32.40710120891885</v>
+        <v>41.49318085298187</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>24.80369269706125</v>
+        <v>16.42129272798803</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.303451799236962</v>
+        <v>1.328853199688669</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-1.147633489802696</v>
+        <v>-1.205374466615639</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6983</v>
+        <v>6894</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>204.6730904988314</v>
+        <v>205.270124785197</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>331</v>
+        <v>327.5</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>40.42800176394482</v>
+        <v>40.5061992426077</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>10.35397433521047</v>
+        <v>16.94169642669102</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.3703668960744277</v>
+        <v>0.6118846872729944</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-1.471053776586746</v>
+        <v>-2.912518678186893</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>7730</v>
+        <v>6906</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>203.7000137330242</v>
+        <v>205.2526191377197</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>171.5</v>
+        <v>72</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>42.9930447495536</v>
+        <v>32.40710120891885</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>15.55739243173198</v>
+        <v>24.80369269706125</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.7227129869499088</v>
+        <v>0.303451799236962</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-1.13054870277062</v>
+        <v>-1.147633489802696</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>7705</v>
+        <v>6983</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>197.3596074567908</v>
+        <v>204.6730904988314</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>30.55</v>
+        <v>331</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>42.88115581773835</v>
+        <v>40.42800176394482</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>17.71905803126853</v>
+        <v>10.35397433521047</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.2809192210757774</v>
+        <v>0.3703668960744277</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0512062695816778</v>
+        <v>-1.471053776586746</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6955</v>
+        <v>7730</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>196.7701736396488</v>
+        <v>203.7000137330241</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>115</v>
+        <v>171.5</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>48.32321003153277</v>
+        <v>42.9930447495536</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>6.135155060467894</v>
+        <v>15.55739243173198</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.0970425574011437</v>
+        <v>0.7227129869499088</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>1.020650435828945</v>
+        <v>-1.13054870277062</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6877</v>
+        <v>7705</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>196.3983698110014</v>
+        <v>197.3596074567908</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>125.5</v>
+        <v>30.55</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>43.60049229304807</v>
+        <v>42.88115581773835</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>14.85333228441051</v>
+        <v>17.71905803126853</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.07375806071026191</v>
+        <v>0.2809192210757774</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0491184698967184</v>
+        <v>-0.0512062695816778</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6859</v>
+        <v>6955</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>194.5084160308808</v>
+        <v>196.7701736396488</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>115</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>28.93112423057605</v>
+        <v>48.32321003153277</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>28.85335980002788</v>
+        <v>6.135155060467894</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.013205249826408</v>
+        <v>0.0970425574011437</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-1.990051030975611</v>
+        <v>1.020650435828945</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6855</v>
+        <v>6877</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>190.5486314561895</v>
+        <v>196.3983698110014</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>115.5</v>
+        <v>125.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>50.96467179730154</v>
+        <v>43.60049229304807</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>6.481467879946938</v>
+        <v>14.85333228441051</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.5965618114964888</v>
+        <v>0.07375806071026191</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.9671137905820668</v>
+        <v>0.0491184698967184</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>7753</v>
+        <v>6859</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>185.7740847359411</v>
+        <v>194.5084160308808</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>40.8</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>44.18940689034861</v>
+        <v>28.93112423057605</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>17.97307038473062</v>
+        <v>28.85335980002788</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.7958563869017407</v>
+        <v>1.013205249826408</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.2202170299596291</v>
+        <v>-1.990051030975611</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6918</v>
+        <v>6855</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>179.94869547194</v>
+        <v>190.5486314561895</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>115.5</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>47.31413961821929</v>
+        <v>50.96467179730154</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>13.7910912916683</v>
+        <v>6.481467879946938</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.4904459625298455</v>
+        <v>0.5965618114964888</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0602000851603133</v>
+        <v>0.9671137905820668</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>7547</v>
+        <v>7753</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>179.4473877781892</v>
+        <v>185.7740847359411</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>52.3</v>
+        <v>40.8</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>30.02228468716925</v>
+        <v>44.18940689034861</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>17.48928897843459</v>
+        <v>17.97307038473062</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.4743380950165185</v>
+        <v>0.7958563869017407</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.1556371386747717</v>
+        <v>-0.2202170299596291</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6988</v>
+        <v>6918</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>178.7902582330885</v>
+        <v>179.94869547194</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>12.9</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>36.33683112670575</v>
+        <v>47.31413961821929</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>14.4570125879655</v>
+        <v>13.7910912916683</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.3971758151702626</v>
+        <v>0.4904459625298455</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0125992961426005</v>
+        <v>-0.0602000851603133</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6890</v>
+        <v>7547</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>171.5786650722937</v>
+        <v>179.4473877781892</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>169</v>
+        <v>52.3</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>36.67751501576336</v>
+        <v>30.02228468716925</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>19.24510628661029</v>
+        <v>17.48928897843459</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.2023577589010086</v>
+        <v>0.4743380950165185</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-3.370399106566367</v>
+        <v>-0.1556371386747717</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6865</v>
+        <v>6988</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>168.73422629968</v>
+        <v>178.7902582330885</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>25.05</v>
+        <v>12.9</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>49.26689104797424</v>
+        <v>36.33683112670575</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>9.845933078330482</v>
+        <v>14.4570125879655</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.08929354980254491</v>
+        <v>0.3971758151702626</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.2074440530167544</v>
+        <v>-0.0125992961426005</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6895</v>
+        <v>6890</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>163.2291494795392</v>
+        <v>171.5786650722937</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>31.81299848777996</v>
+        <v>36.67751501576336</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>30.55073685070182</v>
+        <v>19.24510628661029</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.2717925046859297</v>
+        <v>0.2023577589010086</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-1.074283449431368</v>
+        <v>-3.370399106566367</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6921</v>
+        <v>6865</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>160.136694393625</v>
+        <v>168.73422629968</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>64.90000000000001</v>
+        <v>25.05</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>38.97020580413206</v>
+        <v>49.26689104797424</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>26.43927688226871</v>
+        <v>9.845933078330482</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.2870681194705746</v>
+        <v>0.08929354980254491</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.0961561285328849</v>
+        <v>0.2074440530167544</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>8034</v>
+        <v>6895</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>158.491951559348</v>
+        <v>163.2291494795392</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>19.8</v>
+        <v>124</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>30.3332185645754</v>
+        <v>31.81299848777996</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>34.8415364599805</v>
+        <v>30.55073685070182</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.4029681016091719</v>
+        <v>0.2717925046859297</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0648785332838016</v>
+        <v>-1.074283449431368</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6781,21 +6781,21 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>8038</v>
+        <v>6921</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>158.3054124213667</v>
+        <v>160.136694393625</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>36.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>39.96880987574421</v>
+        <v>38.97020580413206</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>15.9639577951924</v>
+        <v>26.43927688226871</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.3101993186704451</v>
+        <v>0.2870681194705746</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.3794560138838916</v>
+        <v>-0.0961561285328849</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6931</v>
+        <v>8034</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>146.6632521796142</v>
+        <v>158.491951559348</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>39.25</v>
+        <v>19.8</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>40.88809693038144</v>
+        <v>30.3332185645754</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>12.0984226218502</v>
+        <v>34.8415364599805</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.7043380951900878</v>
+        <v>0.4029681016091719</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.0331047490390614</v>
+        <v>-0.0648785332838016</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>7703</v>
+        <v>8038</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>138.8569836433325</v>
+        <v>158.3054124213667</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>187.5</v>
+        <v>36.8</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>42.24381130595751</v>
+        <v>39.96880987574421</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>13.69857975562939</v>
+        <v>15.9639577951924</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.2098593210481578</v>
+        <v>0.3101993186704451</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-1.007432814263354</v>
+        <v>-0.3794560138838916</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>7842</v>
+        <v>6931</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>136.2759186189504</v>
+        <v>146.6632521796142</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>91.59999999999999</v>
+        <v>39.25</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>49.32542451173848</v>
+        <v>40.88809693038144</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>15.69340405427218</v>
+        <v>12.0984226218502</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.1390985866102999</v>
+        <v>0.7043380951900878</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>1.287908924346765</v>
+        <v>0.0331047490390614</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>8044</v>
+        <v>7703</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>134.431100499208</v>
+        <v>138.8569836433325</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>26.45</v>
+        <v>187.5</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>41.90736403198979</v>
+        <v>42.24381130595751</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>15.11553237497101</v>
+        <v>13.69857975562939</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.5008550610459482</v>
+        <v>0.2098593210481578</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.1122944522233092</v>
+        <v>-1.007432814263354</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7046,21 +7046,21 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6925</v>
+        <v>7842</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>114.4396232274868</v>
+        <v>136.2759186189504</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>56.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>40.98340105767107</v>
+        <v>49.32542451173848</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>12.15467813603873</v>
+        <v>15.69340405427218</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.4946361450944301</v>
+        <v>0.1390985866102999</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.0838620329676507</v>
+        <v>1.287908924346765</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>7803</v>
+        <v>8044</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>101.0730754950589</v>
+        <v>134.431100499208</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>20.95</v>
+        <v>26.45</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>35.11625656593348</v>
+        <v>41.90736403198979</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>18.23838331315716</v>
+        <v>15.11553237497101</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.4845551470111316</v>
+        <v>0.5008550610459482</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.1114402098866892</v>
+        <v>-0.1122944522233092</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7152,52 +7152,158 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
+        <v>6925</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>意藍</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>114.4396232274868</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>40.98340105767107</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>12.15467813603873</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.4946361450944301</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>-0.0838620329676507</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>7803</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>雲象科技-創</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>101.0730754950589</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>20.95</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>35.11625656593348</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>18.23838331315716</v>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>0.4845551470111316</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>-0.1114402098866892</v>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
         <v>6908</v>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>宏碁遊戲-創</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D127" s="2" t="n">
+      <c r="C129" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D129" s="2" t="n">
         <v>64.96866177491293</v>
       </c>
-      <c r="E127" s="2" t="n">
+      <c r="E129" s="2" t="n">
         <v>35.75</v>
       </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H127" s="2" t="n">
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H129" s="2" t="n">
         <v>37.27054674164981</v>
       </c>
-      <c r="I127" s="2" t="n">
+      <c r="I129" s="2" t="n">
         <v>19.50756862546607</v>
       </c>
-      <c r="J127" s="2" t="n">
+      <c r="J129" s="2" t="n">
         <v>0.06986455802727889</v>
       </c>
-      <c r="K127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N127" s="2" t="n">
+      <c r="K129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N129" s="2" t="n">
         <v>-0.0531933770981143</v>
       </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="O129" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
